--- a/artfynd/A 25881-2023 artfynd.xlsx
+++ b/artfynd/A 25881-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124273089</v>
+        <v>124273087</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464654</v>
+        <v>464651</v>
       </c>
       <c r="R2" t="n">
-        <v>6780889</v>
+        <v>6780888</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124273087</v>
+        <v>124273089</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +815,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464651</v>
+        <v>464654</v>
       </c>
       <c r="R3" t="n">
-        <v>6780888</v>
+        <v>6780889</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25881-2023 artfynd.xlsx
+++ b/artfynd/A 25881-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124273087</v>
+        <v>124273089</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464651</v>
+        <v>464654</v>
       </c>
       <c r="R2" t="n">
-        <v>6780888</v>
+        <v>6780889</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124273089</v>
+        <v>124273087</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,31 +811,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464654</v>
+        <v>464651</v>
       </c>
       <c r="R3" t="n">
-        <v>6780889</v>
+        <v>6780888</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
